--- a/02_Basic_Excel_for_Data_Analytics/07_Order-of-Operations.xlsx
+++ b/02_Basic_Excel_for_Data_Analytics/07_Order-of-Operations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 COURSES\Learn_Data_Analytics_by_CWH\02_Basic_Excel_for_Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA7598F-63D7-4D53-A2ED-B789645B1112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A20F5D-865F-4FC5-A7C3-C992DF6185BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -181,19 +181,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -201,7 +193,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -484,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="25.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="10.36328125" customWidth="1"/>
@@ -492,34 +490,34 @@
     <col min="10" max="10" width="23.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>23</v>
       </c>
@@ -539,12 +537,10 @@
         <f>1+4*C2</f>
         <v>89</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>4</v>
       </c>
@@ -561,16 +557,15 @@
         <v>7</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -587,54 +582,49 @@
         <v>5</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I5" s="7" t="s">
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I6" s="7" t="s">
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I7" s="7" t="s">
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I8" s="7" t="s">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="4"/>
+      <c r="L8" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
